--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SouthernMoney" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
   <si>
     <t>id</t>
   </si>
@@ -122,16 +122,22 @@
     <t>牌池ID</t>
   </si>
   <si>
-    <t>炸弹倍数</t>
-  </si>
-  <si>
-    <t>剩余普通</t>
-  </si>
-  <si>
-    <t>剩余2</t>
-  </si>
-  <si>
-    <t>剩余炸弹</t>
+    <t>牌局中炸弹倍数</t>
+  </si>
+  <si>
+    <t>结算剩余普通牌的倍数</t>
+  </si>
+  <si>
+    <t>结算剩余手牌2的倍数</t>
+  </si>
+  <si>
+    <t>结算剩余炸弹的倍数</t>
+  </si>
+  <si>
+    <t>结算玩家最终赢分</t>
+  </si>
+  <si>
+    <t>例如</t>
   </si>
   <si>
     <t>int</t>
@@ -170,13 +176,15 @@
     <t>南方前进</t>
   </si>
   <si>
-    <t>2,1;3,1;4,1;6,1;7,1;8,1;10,1</t>
-  </si>
-  <si>
-    <t>2,1;3,1;4,1;6,1</t>
-  </si>
-  <si>
-    <t>7,1;8,1;10,1;12,1;15,1;18,1</t>
+    <t>2;1</t>
+  </si>
+  <si>
+    <t>最终赢分=剩余普通牌赢奖+剩余手牌2赢奖+剩余炸弹赢奖（炸弹结算是在牌局中即时结算）</t>
+  </si>
+  <si>
+    <t>剩余手牌结算：玩家手牌剩5张普通牌，两个2，一个炸弹，押分3000
+玩家赢分=5×1×3000+2×2×3000+1×4×3000
+牌局中炸弹结算：ABCD四个玩家，A被B炸了，B被C炸了，C被D炸了，最终赢家为D，输家为AC,其中A赔付2倍押分，C赔付1倍押分（就相当于多个炸弹出现时，只有第一个被炸玩家和倒数第二个炸弹玩家为输家）</t>
   </si>
 </sst>
 </file>
@@ -814,7 +822,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -826,6 +834,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1138,8 +1152,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6"/>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
@@ -1148,10 +1162,13 @@
     <col min="5" max="5" width="31.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
     <col min="7" max="7" width="18.875" customWidth="1"/>
+    <col min="8" max="8" width="19.025" customWidth="1"/>
     <col min="9" max="10" width="18.875" customWidth="1"/>
+    <col min="11" max="11" width="26.6666666666667" customWidth="1"/>
+    <col min="12" max="12" width="58.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1182,172 +1199,193 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>300400</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F4" s="1">
+        <v>100003</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3">
+        <v>4</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2">
         <v>300400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2</v>
       </c>
       <c r="E5" s="3">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="F5" s="1">
         <v>100003</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" s="3">
         <v>1</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="I5" s="3">
+        <v>2</v>
+      </c>
+      <c r="J5" s="3">
+        <v>4</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2">
         <v>300400</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="F6" s="1">
         <v>100003</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H6" s="3">
         <v>1</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="I6" s="3">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3">
+        <v>4</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2">
-        <v>300400</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="1">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F7" s="1">
-        <v>100003</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>24</v>
-      </c>
+    <row r="7" spans="1:12">
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="L9" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="L4:L6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
   <si>
     <t>id</t>
   </si>
@@ -822,7 +822,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -837,9 +837,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1155,7 +1152,7 @@
   <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
@@ -1268,7 +1265,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1">
-        <v>1</v>
+        <v>3004001</v>
       </c>
       <c r="B4" s="2">
         <v>300400</v>
@@ -1306,7 +1303,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1">
-        <v>2</v>
+        <v>3004002</v>
       </c>
       <c r="B5" s="2">
         <v>300400</v>
@@ -1340,7 +1337,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1">
-        <v>3</v>
+        <v>3004003</v>
       </c>
       <c r="B6" s="2">
         <v>300400</v>
@@ -1373,18 +1370,117 @@
       <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="L7" s="5"/>
+      <c r="A7" s="1">
+        <v>30040010</v>
+      </c>
+      <c r="B7" s="2">
+        <v>300400</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F7" s="1">
+        <v>100003</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
+        <v>2</v>
+      </c>
+      <c r="J7" s="3">
+        <v>4</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="L8" s="5"/>
+      <c r="A8" s="1">
+        <v>30040011</v>
+      </c>
+      <c r="B8" s="2">
+        <v>300400</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F8" s="1">
+        <v>100003</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2</v>
+      </c>
+      <c r="J8" s="3">
+        <v>4</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="L9" s="5"/>
+      <c r="A9" s="1">
+        <v>30040012</v>
+      </c>
+      <c r="B9" s="2">
+        <v>300400</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F9" s="1">
+        <v>100003</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <v>2</v>
+      </c>
+      <c r="J9" s="3">
+        <v>4</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
     <mergeCell ref="L4:L6"/>
+    <mergeCell ref="L7:L9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SouthernMoney" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
   <si>
     <t>id</t>
   </si>
@@ -144,9 +144,6 @@
   </si>
   <si>
     <t>List&lt;int&gt;{;}</t>
-  </si>
-  <si>
-    <t>list&lt;list&lt;int&gt;{,}&gt;{;}</t>
   </si>
   <si>
     <t>gameId</t>
@@ -361,12 +358,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1149,7 +1146,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
@@ -1215,22 +1212,22 @@
         <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1238,90 +1235,64 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1">
-        <v>3004001</v>
-      </c>
-      <c r="B4" s="2">
-        <v>300400</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F4" s="1">
-        <v>100003</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2</v>
-      </c>
-      <c r="J4" s="3">
-        <v>4</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1">
-        <v>3004002</v>
+        <v>3004001</v>
       </c>
       <c r="B5" s="2">
         <v>300400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
       </c>
       <c r="E5" s="3">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="F5" s="1">
         <v>100003</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="3">
         <v>1</v>
@@ -1332,30 +1303,34 @@
       <c r="J5" s="3">
         <v>4</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
+      <c r="K5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1">
-        <v>3004003</v>
+        <v>3004002</v>
       </c>
       <c r="B6" s="2">
         <v>300400</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="3">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="F6" s="1">
         <v>100003</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H6" s="3">
         <v>1</v>
@@ -1371,25 +1346,25 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1">
-        <v>30040010</v>
+        <v>3004003</v>
       </c>
       <c r="B7" s="2">
         <v>300400</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
       </c>
       <c r="E7" s="3">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="F7" s="1">
         <v>100003</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" s="3">
         <v>1</v>
@@ -1400,34 +1375,30 @@
       <c r="J7" s="3">
         <v>4</v>
       </c>
-      <c r="K7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1">
-        <v>30040011</v>
+        <v>30040010</v>
       </c>
       <c r="B8" s="2">
         <v>300400</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="1">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
       </c>
       <c r="E8" s="3">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="F8" s="1">
         <v>100003</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H8" s="3">
         <v>1</v>
@@ -1438,30 +1409,34 @@
       <c r="J8" s="3">
         <v>4</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="K8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1">
-        <v>30040012</v>
+        <v>30040011</v>
       </c>
       <c r="B9" s="2">
         <v>300400</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="3">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="F9" s="1">
         <v>100003</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H9" s="3">
         <v>1</v>
@@ -1475,12 +1450,46 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="1">
+        <v>30040012</v>
+      </c>
+      <c r="B10" s="2">
+        <v>300400</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F10" s="1">
+        <v>100003</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2</v>
+      </c>
+      <c r="J10" s="3">
+        <v>4</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="L4:L6"/>
-    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="K5:K7"/>
+    <mergeCell ref="K8:K10"/>
+    <mergeCell ref="L5:L7"/>
+    <mergeCell ref="L8:L10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SouthernMoney" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="G1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
+    <comment ref="H1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -79,20 +79,30 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">赢奖 = 剩余2的张数 * 每张倍数 * 总投
+          <t xml:space="preserve">赢奖 = 剩余红2的张数 * 每张倍数 * 总投
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1">
+    <comment ref="I1" authorId="1">
       <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">赢奖 = 剩余炸弹个数 * 每个炸弹倍数 * 总投
+          <t xml:space="preserve">
+赢奖 = 剩余黑2的张数 * 每张倍数 * 总投
 </t>
         </r>
       </text>
@@ -102,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>id</t>
   </si>
@@ -122,16 +132,22 @@
     <t>牌池ID</t>
   </si>
   <si>
-    <t>牌局中炸弹倍数</t>
-  </si>
-  <si>
     <t>结算剩余普通牌的倍数</t>
   </si>
   <si>
-    <t>结算剩余手牌2的倍数</t>
-  </si>
-  <si>
-    <t>结算剩余炸弹的倍数</t>
+    <t>结算剩余手牌红2的倍数</t>
+  </si>
+  <si>
+    <t>结算剩余手牌黑2的倍数</t>
+  </si>
+  <si>
+    <t>被管炸弹的倍数（三连对）</t>
+  </si>
+  <si>
+    <t>被管炸弹的倍数（四条）</t>
+  </si>
+  <si>
+    <t>被管炸弹的倍数（四连对）</t>
   </si>
   <si>
     <t>结算玩家最终赢分</t>
@@ -143,9 +159,6 @@
     <t>int</t>
   </si>
   <si>
-    <t>List&lt;int&gt;{;}</t>
-  </si>
-  <si>
     <t>gameId</t>
   </si>
   <si>
@@ -158,13 +171,13 @@
     <t>poolId</t>
   </si>
   <si>
-    <t>boomMultiple</t>
-  </si>
-  <si>
     <t>remainNormal</t>
   </si>
   <si>
-    <t>remain2</t>
+    <t>remainred2</t>
+  </si>
+  <si>
+    <t>remainblack2</t>
   </si>
   <si>
     <t>remainBoom</t>
@@ -173,15 +186,12 @@
     <t>南方前进</t>
   </si>
   <si>
-    <t>2;1</t>
-  </si>
-  <si>
     <t>最终赢分=剩余普通牌赢奖+剩余手牌2赢奖+剩余炸弹赢奖（炸弹结算是在牌局中即时结算）</t>
   </si>
   <si>
-    <t>剩余手牌结算：玩家手牌剩5张普通牌，两个2，一个炸弹，押分3000
-玩家赢分=5×1×3000+2×2×3000+1×4×3000
-牌局中炸弹结算：ABCD四个玩家，A被B炸了，B被C炸了，C被D炸了，最终赢家为D，输家为AC,其中A赔付2倍押分，C赔付1倍押分（就相当于多个炸弹出现时，只有第一个被炸玩家和倒数第二个炸弹玩家为输家）</t>
+    <t>剩余手牌结算：玩家手牌剩10张牌，一个红2，一个黑2，一个四条炸弹，押分3000
+玩家赢分=10×1×3000+4×3000+2×3000+1×8×3000
+牌局中炸弹结算：ABCD四个玩家，A出了一个红2，然后被B的三连对炸弹炸了，B被C四条炸弹炸了，C被D四连对炸弹炸了，D被A更大的四连对炸弹炸了，最终赢家为A，输家为D,并且赔付此轮所有的输分（包括A出的红2，B出的三连对，C出的四条，D出的四连对，都算在D的头上）</t>
   </si>
 </sst>
 </file>
@@ -1146,23 +1156,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="31.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="18.875" customWidth="1"/>
-    <col min="8" max="8" width="19.025" customWidth="1"/>
-    <col min="9" max="10" width="18.875" customWidth="1"/>
-    <col min="11" max="11" width="26.6666666666667" customWidth="1"/>
-    <col min="12" max="12" width="58.75" customWidth="1"/>
+    <col min="7" max="7" width="19.025" customWidth="1"/>
+    <col min="8" max="9" width="18.875" customWidth="1"/>
+    <col min="10" max="10" width="22.3583333333333" customWidth="1"/>
+    <col min="11" max="11" width="21.525" customWidth="1"/>
+    <col min="12" max="12" width="23.3333333333333" customWidth="1"/>
+    <col min="13" max="13" width="26.6666666666667" customWidth="1"/>
+    <col min="14" max="14" width="58.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1199,68 +1211,77 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:14">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1272,7 +1293,7 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:14">
       <c r="A5" s="1">
         <v>3004001</v>
       </c>
@@ -1280,7 +1301,7 @@
         <v>300400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1291,26 +1312,32 @@
       <c r="F5" s="1">
         <v>100003</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>23</v>
+      <c r="G5" s="3">
+        <v>1</v>
       </c>
       <c r="H5" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" s="3">
         <v>2</v>
       </c>
       <c r="J5" s="3">
-        <v>4</v>
-      </c>
-      <c r="K5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="4">
+        <v>8</v>
+      </c>
+      <c r="L5" s="4">
+        <v>10</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="N5" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:14">
       <c r="A6" s="1">
         <v>3004002</v>
       </c>
@@ -1318,7 +1345,7 @@
         <v>300400</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -1329,22 +1356,28 @@
       <c r="F6" s="1">
         <v>100003</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>23</v>
+      <c r="G6" s="3">
+        <v>1</v>
       </c>
       <c r="H6" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" s="3">
         <v>2</v>
       </c>
       <c r="J6" s="3">
-        <v>4</v>
-      </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="K6" s="4">
+        <v>8</v>
+      </c>
+      <c r="L6" s="4">
+        <v>10</v>
+      </c>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:14">
       <c r="A7" s="1">
         <v>3004003</v>
       </c>
@@ -1352,7 +1385,7 @@
         <v>300400</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1363,22 +1396,28 @@
       <c r="F7" s="1">
         <v>100003</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>23</v>
+      <c r="G7" s="3">
+        <v>1</v>
       </c>
       <c r="H7" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7" s="3">
         <v>2</v>
       </c>
       <c r="J7" s="3">
-        <v>4</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="K7" s="4">
+        <v>8</v>
+      </c>
+      <c r="L7" s="4">
+        <v>10</v>
+      </c>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:14">
       <c r="A8" s="1">
         <v>30040010</v>
       </c>
@@ -1386,7 +1425,7 @@
         <v>300400</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -1397,26 +1436,32 @@
       <c r="F8" s="1">
         <v>100003</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>23</v>
+      <c r="G8" s="3">
+        <v>1</v>
       </c>
       <c r="H8" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8" s="3">
         <v>2</v>
       </c>
       <c r="J8" s="3">
-        <v>4</v>
-      </c>
-      <c r="K8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="4">
+        <v>8</v>
+      </c>
+      <c r="L8" s="4">
+        <v>10</v>
+      </c>
+      <c r="M8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="N8" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:14">
       <c r="A9" s="1">
         <v>30040011</v>
       </c>
@@ -1424,7 +1469,7 @@
         <v>300400</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -1435,22 +1480,28 @@
       <c r="F9" s="1">
         <v>100003</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>23</v>
+      <c r="G9" s="3">
+        <v>1</v>
       </c>
       <c r="H9" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" s="3">
         <v>2</v>
       </c>
       <c r="J9" s="3">
-        <v>4</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="K9" s="4">
+        <v>8</v>
+      </c>
+      <c r="L9" s="4">
+        <v>10</v>
+      </c>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:14">
       <c r="A10" s="1">
         <v>30040012</v>
       </c>
@@ -1458,7 +1509,7 @@
         <v>300400</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -1469,27 +1520,33 @@
       <c r="F10" s="1">
         <v>100003</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>23</v>
+      <c r="G10" s="3">
+        <v>1</v>
       </c>
       <c r="H10" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" s="3">
         <v>2</v>
       </c>
       <c r="J10" s="3">
-        <v>4</v>
-      </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="K10" s="4">
+        <v>8</v>
+      </c>
+      <c r="L10" s="4">
+        <v>10</v>
+      </c>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="K5:K7"/>
-    <mergeCell ref="K8:K10"/>
-    <mergeCell ref="L5:L7"/>
-    <mergeCell ref="L8:L10"/>
+    <mergeCell ref="M5:M7"/>
+    <mergeCell ref="M8:M10"/>
+    <mergeCell ref="N5:N7"/>
+    <mergeCell ref="N8:N10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -181,6 +181,12 @@
   </si>
   <si>
     <t>remainBoom</t>
+  </si>
+  <si>
+    <t>fourkindboom</t>
+  </si>
+  <si>
+    <t>fourpairsboom</t>
   </si>
   <si>
     <t>南方前进</t>
@@ -368,12 +374,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1250,6 +1256,9 @@
       <c r="K2" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="L2" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
@@ -1279,6 +1288,12 @@
       </c>
       <c r="J3" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1301,7 +1316,7 @@
         <v>300400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1331,10 +1346,10 @@
         <v>10</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1345,7 +1360,7 @@
         <v>300400</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -1385,7 +1400,7 @@
         <v>300400</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1425,7 +1440,7 @@
         <v>300400</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -1455,10 +1470,10 @@
         <v>10</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1469,7 +1484,7 @@
         <v>300400</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -1509,7 +1524,7 @@
         <v>300400</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>

--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SouthernMoney" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
   <si>
     <t>id</t>
   </si>
@@ -141,6 +141,15 @@
     <t>结算剩余手牌黑2的倍数</t>
   </si>
   <si>
+    <t>结算剩余炸弹的倍数（三连对）</t>
+  </si>
+  <si>
+    <t>结算剩余炸弹的倍数（四条）</t>
+  </si>
+  <si>
+    <t>结算剩余炸弹的倍数（四连对）</t>
+  </si>
+  <si>
     <t>被管炸弹的倍数（三连对）</t>
   </si>
   <si>
@@ -178,6 +187,15 @@
   </si>
   <si>
     <t>remainblack2</t>
+  </si>
+  <si>
+    <t>remainBoom1</t>
+  </si>
+  <si>
+    <t>fourkindboom1</t>
+  </si>
+  <si>
+    <t>fourpairsboom1</t>
   </si>
   <si>
     <t>remainBoom</t>
@@ -1162,7 +1180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
@@ -1174,13 +1192,16 @@
     <col min="7" max="7" width="19.025" customWidth="1"/>
     <col min="8" max="9" width="18.875" customWidth="1"/>
     <col min="10" max="10" width="22.3583333333333" customWidth="1"/>
-    <col min="11" max="11" width="21.525" customWidth="1"/>
-    <col min="12" max="12" width="23.3333333333333" customWidth="1"/>
-    <col min="13" max="13" width="26.6666666666667" customWidth="1"/>
-    <col min="14" max="14" width="58.75" customWidth="1"/>
+    <col min="11" max="11" width="25.6916666666667" customWidth="1"/>
+    <col min="12" max="12" width="30.9666666666667" customWidth="1"/>
+    <col min="13" max="13" width="26.1083333333333" customWidth="1"/>
+    <col min="14" max="14" width="21.525" customWidth="1"/>
+    <col min="15" max="15" width="23.3333333333333" customWidth="1"/>
+    <col min="16" max="16" width="26.6666666666667" customWidth="1"/>
+    <col min="17" max="17" width="58.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1223,80 +1244,107 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:17">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1307,8 +1355,11 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:17">
       <c r="A5" s="1">
         <v>3004001</v>
       </c>
@@ -1316,7 +1367,7 @@
         <v>300400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1345,14 +1396,23 @@
       <c r="L5" s="4">
         <v>10</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>27</v>
+      <c r="M5" s="3">
+        <v>6</v>
+      </c>
+      <c r="N5" s="4">
+        <v>8</v>
+      </c>
+      <c r="O5" s="4">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:17">
       <c r="A6" s="1">
         <v>3004002</v>
       </c>
@@ -1360,7 +1420,7 @@
         <v>300400</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -1389,10 +1449,19 @@
       <c r="L6" s="4">
         <v>10</v>
       </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
+      <c r="M6" s="3">
+        <v>6</v>
+      </c>
+      <c r="N6" s="4">
+        <v>8</v>
+      </c>
+      <c r="O6" s="4">
+        <v>10</v>
+      </c>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:17">
       <c r="A7" s="1">
         <v>3004003</v>
       </c>
@@ -1400,7 +1469,7 @@
         <v>300400</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1429,10 +1498,19 @@
       <c r="L7" s="4">
         <v>10</v>
       </c>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
+      <c r="M7" s="3">
+        <v>6</v>
+      </c>
+      <c r="N7" s="4">
+        <v>8</v>
+      </c>
+      <c r="O7" s="4">
+        <v>10</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:17">
       <c r="A8" s="1">
         <v>30040010</v>
       </c>
@@ -1440,7 +1518,7 @@
         <v>300400</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -1469,14 +1547,23 @@
       <c r="L8" s="4">
         <v>10</v>
       </c>
-      <c r="M8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>27</v>
+      <c r="M8" s="3">
+        <v>6</v>
+      </c>
+      <c r="N8" s="4">
+        <v>8</v>
+      </c>
+      <c r="O8" s="4">
+        <v>10</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:17">
       <c r="A9" s="1">
         <v>30040011</v>
       </c>
@@ -1484,7 +1571,7 @@
         <v>300400</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -1513,10 +1600,19 @@
       <c r="L9" s="4">
         <v>10</v>
       </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
+      <c r="M9" s="3">
+        <v>6</v>
+      </c>
+      <c r="N9" s="4">
+        <v>8</v>
+      </c>
+      <c r="O9" s="4">
+        <v>10</v>
+      </c>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:17">
       <c r="A10" s="1">
         <v>30040012</v>
       </c>
@@ -1524,7 +1620,7 @@
         <v>300400</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -1553,15 +1649,24 @@
       <c r="L10" s="4">
         <v>10</v>
       </c>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
+      <c r="M10" s="3">
+        <v>6</v>
+      </c>
+      <c r="N10" s="4">
+        <v>8</v>
+      </c>
+      <c r="O10" s="4">
+        <v>10</v>
+      </c>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M5:M7"/>
-    <mergeCell ref="M8:M10"/>
-    <mergeCell ref="N5:N7"/>
-    <mergeCell ref="N8:N10"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="P8:P10"/>
+    <mergeCell ref="Q5:Q7"/>
+    <mergeCell ref="Q8:Q10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SouthernMoney" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -141,15 +141,6 @@
     <t>结算剩余手牌黑2的倍数</t>
   </si>
   <si>
-    <t>结算剩余炸弹的倍数（三连对）</t>
-  </si>
-  <si>
-    <t>结算剩余炸弹的倍数（四条）</t>
-  </si>
-  <si>
-    <t>结算剩余炸弹的倍数（四连对）</t>
-  </si>
-  <si>
     <t>被管炸弹的倍数（三连对）</t>
   </si>
   <si>
@@ -187,15 +178,6 @@
   </si>
   <si>
     <t>remainblack2</t>
-  </si>
-  <si>
-    <t>remainBoom1</t>
-  </si>
-  <si>
-    <t>fourkindboom1</t>
-  </si>
-  <si>
-    <t>fourpairsboom1</t>
   </si>
   <si>
     <t>remainBoom</t>
@@ -1180,7 +1162,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
@@ -1192,16 +1174,13 @@
     <col min="7" max="7" width="19.025" customWidth="1"/>
     <col min="8" max="9" width="18.875" customWidth="1"/>
     <col min="10" max="10" width="22.3583333333333" customWidth="1"/>
-    <col min="11" max="11" width="25.6916666666667" customWidth="1"/>
-    <col min="12" max="12" width="30.9666666666667" customWidth="1"/>
-    <col min="13" max="13" width="26.1083333333333" customWidth="1"/>
-    <col min="14" max="14" width="21.525" customWidth="1"/>
-    <col min="15" max="15" width="23.3333333333333" customWidth="1"/>
-    <col min="16" max="16" width="26.6666666666667" customWidth="1"/>
-    <col min="17" max="17" width="58.75" customWidth="1"/>
+    <col min="11" max="11" width="21.525" customWidth="1"/>
+    <col min="12" max="12" width="23.3333333333333" customWidth="1"/>
+    <col min="13" max="13" width="26.6666666666667" customWidth="1"/>
+    <col min="14" max="14" width="58.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1244,107 +1223,80 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:14">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1355,11 +1307,8 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:14">
       <c r="A5" s="1">
         <v>3004001</v>
       </c>
@@ -1367,7 +1316,7 @@
         <v>300400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1396,23 +1345,14 @@
       <c r="L5" s="4">
         <v>10</v>
       </c>
-      <c r="M5" s="3">
-        <v>6</v>
-      </c>
-      <c r="N5" s="4">
-        <v>8</v>
-      </c>
-      <c r="O5" s="4">
-        <v>10</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>33</v>
+      <c r="M5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:14">
       <c r="A6" s="1">
         <v>3004002</v>
       </c>
@@ -1420,7 +1360,7 @@
         <v>300400</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -1449,19 +1389,10 @@
       <c r="L6" s="4">
         <v>10</v>
       </c>
-      <c r="M6" s="3">
-        <v>6</v>
-      </c>
-      <c r="N6" s="4">
-        <v>8</v>
-      </c>
-      <c r="O6" s="4">
-        <v>10</v>
-      </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:14">
       <c r="A7" s="1">
         <v>3004003</v>
       </c>
@@ -1469,7 +1400,7 @@
         <v>300400</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1498,19 +1429,10 @@
       <c r="L7" s="4">
         <v>10</v>
       </c>
-      <c r="M7" s="3">
-        <v>6</v>
-      </c>
-      <c r="N7" s="4">
-        <v>8</v>
-      </c>
-      <c r="O7" s="4">
-        <v>10</v>
-      </c>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:14">
       <c r="A8" s="1">
         <v>30040010</v>
       </c>
@@ -1518,7 +1440,7 @@
         <v>300400</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -1547,23 +1469,14 @@
       <c r="L8" s="4">
         <v>10</v>
       </c>
-      <c r="M8" s="3">
-        <v>6</v>
-      </c>
-      <c r="N8" s="4">
-        <v>8</v>
-      </c>
-      <c r="O8" s="4">
-        <v>10</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>33</v>
+      <c r="M8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:14">
       <c r="A9" s="1">
         <v>30040011</v>
       </c>
@@ -1571,7 +1484,7 @@
         <v>300400</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -1600,19 +1513,10 @@
       <c r="L9" s="4">
         <v>10</v>
       </c>
-      <c r="M9" s="3">
-        <v>6</v>
-      </c>
-      <c r="N9" s="4">
-        <v>8</v>
-      </c>
-      <c r="O9" s="4">
-        <v>10</v>
-      </c>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:14">
       <c r="A10" s="1">
         <v>30040012</v>
       </c>
@@ -1620,7 +1524,7 @@
         <v>300400</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -1649,24 +1553,15 @@
       <c r="L10" s="4">
         <v>10</v>
       </c>
-      <c r="M10" s="3">
-        <v>6</v>
-      </c>
-      <c r="N10" s="4">
-        <v>8</v>
-      </c>
-      <c r="O10" s="4">
-        <v>10</v>
-      </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="P5:P7"/>
-    <mergeCell ref="P8:P10"/>
-    <mergeCell ref="Q5:Q7"/>
-    <mergeCell ref="Q8:Q10"/>
+    <mergeCell ref="M5:M7"/>
+    <mergeCell ref="M8:M10"/>
+    <mergeCell ref="N5:N7"/>
+    <mergeCell ref="N8:N10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
